--- a/artfynd/A 25485-2025 artfynd.xlsx
+++ b/artfynd/A 25485-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>81745389</v>
+        <v>81745487</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bickberg, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>387244.154411255</v>
+        <v>387115</v>
       </c>
       <c r="R2" t="n">
-        <v>6652775.944846557</v>
+        <v>6652822</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +746,14 @@
           <t>2019-10-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-10-02</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134057883</v>
+        <v>134057898</v>
       </c>
       <c r="B3" t="n">
-        <v>8449</v>
+        <v>80489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>386946</v>
+        <v>387114</v>
       </c>
       <c r="R3" t="n">
-        <v>6652809</v>
+        <v>6652815</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -881,6 +875,597 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>81745389</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bickberg, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>387244</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6652776</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2019-10-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2019-10-02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>81745477</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bickberg, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>386721</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6652826</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2019-10-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2019-10-02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>81745534</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bickberg, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>387149</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6652820</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2019-10-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2019-10-02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>81745545</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bickberg, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>387153</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6652817</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2019-10-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2019-10-02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>81745489</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bickberg, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>387115</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6652822</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-10-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-10-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På björk.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134057883</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Björnhöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>386946</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6652809</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Max Ljungkvist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Max Ljungkvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
